--- a/output/(山本)可読性_表記適切性_再構成.xlsx
+++ b/output/(山本)可読性_表記適切性_再構成.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26.13" customWidth="1" min="1" max="1"/>
@@ -461,13 +461,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>文書全体、または章・節などの論理単位において、敬体（です・ます調）または常体（である調）のいずれか一方を選択し、混在させずに記述している。</t>
+          <t>プロジェクトの文書執筆規約に基づき、文書全体の文末表現を常体（だ・である調）または敬体（です・ます調）のいずれか一方に統一している。</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】本機能は情報の検索を行います。また、結果を一覧で表示する。（「です・ます調」と「である調」が混在している）。
-→【適合例】本機能は情報の検索を行います。また、結果を一覧で表示します。</t>
+          <t>★新規追加
+【非適合例】本システムは、ユーザ情報を管理する。また、パスワードの有効期限は90日としています。（非適合の理由：同一段落内で常体と敬体が混在している。）
+→【適合例】本システムは、ユーザ情報を管理する。また、パスワードの有効期限は90日としている。</t>
         </is>
       </c>
     </row>
@@ -479,51 +480,52 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>同一の対象、概念、または動作を示す言葉について、全編を通じて表記（漢字、ひらがな、カタカナ、英数字）の揺れを排除し、一貫した表記を選択している。</t>
+          <t>プロジェクトの用語定義集や表記ガイドラインに準拠し、同一文書内で同義語の表記揺れ（外来語の長音符、送り仮名、アルファベットの大文字小文字など）を発生させず、単一の表記を採用している。</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】画面上のユーザをクリックすると、ユーザー詳細が表示される。（「ユーザ」と「ユーザー」の表記が同一文書内で混在している）。
-→【適合例】画面上のユーザーをクリックすると、ユーザー詳細が表示される。</t>
+          <t>★新規追加
+【非適合例】データベースサーバの構築後、Webサーバーとの通信確認を行う。（非適合の理由：同一文内で外来語の長音符の有無が混在している。）
+→【適合例】データベースサーバの構築後、Webサーバとの通信確認を行う。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>用語および表記法を統一している</t>
+          <t>用語を使い分けている</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>同一の対象や処理を指す語彙が揺れないよう、用語定義集や標準的な技術用語に基づき、文脈に応じた名称を厳密に統一して記述している。</t>
+          <t>文書の想定読者（顧客、外部ベンダ、運用担当者など）のITリテラシやドメイン知識を定義したうえで、組織内でのみ通用する隠語を排除し、読者層が正確に理解できる標準的な用語へ置換している。</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】データをサーバに保存した後、当該レコードをコミットする。（「保存」と「コミット」が同じ動作を指して混在している）。
-→【適合例】データをサーバに保存した後、当該レコードを保存する。</t>
+【非適合例】夜間バッチがコケた場合、シス管にアラートを飛ばす。（非適合の理由：顧客や外部ベンダが閲覧する文書において、組織内の隠語や略語を使用している。）
+→【適合例】夜間バッチ処理が異常終了した場合、システム管理者にアラート通知を行う。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>用語を使い分けている</t>
+          <t>用語（専門用語，略語など）および記号を定義している（「再利用性」に関連）</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>読者の専門性や立場を考慮し、未定義の社内略語や専門用語（ジャーゴン）を避け、対象読者が共通して理解できる一般的な用語を選択して記述している。</t>
+          <t>文書内で使用する専門用語や略語について、初出時にフルスペルと意味を併記するか、プロジェクト共通の用語定義集への参照を明記し、読者による解釈のブレを防止している。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】本件のASISにおけるボトルネックは、ホスト側のバッチ処理にある。（社外の読み手に対して「ASIS」などの専門用語を説明なしに使用している）。
-→【適合例】本システムの現状（As-Is）における問題点は、基幹システムのバッチ処理にある。</t>
+【非適合例】本機能は、BFF層でデータの集約処理を行う。（非適合の理由：専門的な略語が初出時にフルスペルや意味の定義なしに使用されている。）
+→【適合例】本機能は、BFF（Backends For Frontends）層でデータの集約処理を行う。</t>
         </is>
       </c>
     </row>
@@ -535,32 +537,33 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>独自の意味を持つ専門用語、略語、記号について、初出箇所または用語定義セクションにおいて、正式名称や定義内容を明記している。</t>
+          <t>閾値や制約事項を示す条件式について、曖昧な記号（波線など）を排除し、数値の境界条件（以上、以下、未満、より大きいなど）を解釈の余地がない厳密な言語表現で定義している。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】APIを利用してデータを取得する。（「API」という略語の定義や正式名称が文書内に明記されていない）。
-→【適合例】Application Programming Interface（以下、API）を利用してデータを取得する。</t>
+【非適合例】パスワードの文字数は8文字〜16文字とする。（非適合の理由：波線記号を使用しており、境界値を含むかどうかが曖昧である。）
+→【適合例】パスワードの文字数は8文字以上16文字以下とする。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>用語（専門用語，略語など）および記号を定義している（「再利用性」に関連）</t>
+          <t>用字用語が適切である</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>判定条件や仕様に含まれる値の範囲において、境界値（以上、以下、未満、超）や単位、および特殊な演算記号の意味を一義的に定義している。</t>
+          <t>日本語で表現可能な一般的な動作や状態について、読解を妨げるIT業界特有のカタカナ語を排除し、標準的な和語や漢語に置き換えて記述している。</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】大容量のファイルを送信する場合は注意が必要である。（「大容量」が具体的に何バイト以上を指すか定義されていない）。
-→【適合例】100MB以上のファイル（以下、大容量ファイル）を送信する場合は、事前に管理者へ通知する。</t>
+          <t>★新規追加
+【非適合例】要件定義でアグリーした仕様をベースに設計をフィックスする。（非適合の理由：日本語で表現できる動作に対して、不必要なカタカナ語を使用している。）
+→【適合例】要件定義で合意した仕様に基づき、設計を確定する。</t>
         </is>
       </c>
     </row>
@@ -572,13 +575,14 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>一般的な日本語で表現可能な語彙について、過度なカタカナ語や外来語の使用を抑制し、文脈に応じた平易かつ正確な日本語を選択して記述している。</t>
+          <t>接続詞、副詞、補助動詞などの表記において、JTF日本語標準スタイルガイドや「公用文作成の考え方」に準拠し、漢字ではなくひらがなを使用している。</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>【非適合例】本プロジェクトのスキームをアグリーした後にアサインを行う。（不必要なカタカナ表現により、文の意図が不明瞭になっている）。
-→【適合例】本プロジェクトの計画に合意した後に、担当者の割り当てを行う。</t>
+          <t>★新規追加
+【非適合例】サーバを停止する際は、予めユーザへ告知する。（非適合の理由：スタイルガイドでひらがな表記が推奨されている副詞を漢字で表記している。）
+→【適合例】サーバを停止する際は、あらかじめユーザへ告知する。</t>
         </is>
       </c>
     </row>
@@ -590,89 +594,33 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>補助動詞、形式名詞、接続詞など、公用文やJTFスタイルガイドにおいて「ひらがな表記」が推奨されている語彙を適切に使い分けて記述している。</t>
+          <t>一般的な用字用語集（記者ハンドブックなど）やプロジェクト固有の執筆ルールに基づき、同音異義語や類義語の中から、文脈の意図を正確に伝達する漢字や用語を選択している。</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】データの入力、及び、保存を併せて行う。（「及び」「併せて」など、ひらがな表記が推奨される語彙を漢字で記述している）。
-→【適合例】データの入力、および、保存をあわせて行う。</t>
+【非適合例】システム障害によって発生した顧客の損害を保障する。（非適合の理由：損害を金銭で埋め合わせる意味である「補償」ではなく、権利を守る意味の「保障」を誤用している。）
+→【適合例】システム障害によって発生した顧客の損害を補償する。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>用字用語が適切である</t>
+          <t>記号類・括弧類を適切に使用している</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>組織やプロジェクトで採用している標準的な用字用語集（記者ハンドブック等）や独自の規程に従い、日付、数値、単位等の表記ルールを遵守している。</t>
+          <t>プロジェクトのドキュメント規約に基づき、全角の括弧類と半角の引用符を、画面名、ボタン名、ソースコードの文字列リテラルなどの対象要素ごとに厳密に使い分けている。</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>★新規追加
-【非適合例】日付は2024/03/25と記載する。（プロジェクト規定で「YYYY年MM月DD日」形式と定められているが、異なる形式で記述している）。
-→【適合例】日付は2024年03月25日と記載する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>用字用語が適切である</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>複数の意味を持つ曖昧な語を排除し、その文脈において最も正確な動作や状態を示す具体的な技術用語（物理削除、論理削除等）を選択して記述している。</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>★新規追加
-【非適合例】保存期間を過ぎた古いデータを消す。（「消す」という表現が、物理削除なのか論理削除なのか不明確である）。
-→【適合例】保存期間を過ぎたデータを物理削除する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>記号類・括弧類を適切に使用している</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>引用、強調、変数、入力値など、目的ごとに使用する記号（「」、（）、『』、“”）の役割を定義し、そのルールに従って厳格に使い分けて記述している。</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>【非適合例】ユーザー名は「Admin」とし、パスワードは（password）とする。（同じ入力値の明示に対して異なる括弧を混用している）。
-→【適合例】ユーザー名は「Admin」とし、パスワードは「password」とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>記号類・括弧類を適切に使用している</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>類似した形状を持つ記号（クォート、ハイフン、ダッシュ等）について、文字コードや用途の違いを判別し、技術的に正しい記号を選択して記述している。</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>★新規追加
-【非適合例】SQL文の条件に‘Admin’を指定する。（スマートクォートなど、プログラム実行時にエラーとなる記号を使用している）。
-→【適合例】SQL文の条件に 'Admin' を指定する。</t>
+【非適合例】設定ファイルのキー名として“timeout"を指定する。（非適合の理由：文字列リテラルを囲む記号に、全角のカーリークォートと半角のストレートクォートが混在している。）
+→【適合例】設定ファイルのキー名として"timeout"を指定する。</t>
         </is>
       </c>
     </row>
